--- a/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por otros motivos</t>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,67</t>
+          <t>0,0; 79,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,4</t>
+          <t>0,0; 66,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 9,09</t>
+          <t>0,78; 8,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,43</t>
+          <t>1,2; 11,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,33</t>
+          <t>2,31; 10,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,79</t>
+          <t>0,79; 8,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,21</t>
+          <t>2,34; 11,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,28</t>
+          <t>1,56; 6,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,57</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,48</t>
+          <t>2,4; 8,63</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,21</t>
+          <t>1,35; 6,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,02</t>
+          <t>0,48; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,05</t>
+          <t>0,3; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,98</t>
+          <t>0,26; 3,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,92</t>
+          <t>0,93; 3,71</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,45</t>
+          <t>0,39; 3,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,33</t>
+          <t>0,42; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,22</t>
+          <t>1,56; 6,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,52</t>
+          <t>0,54; 5,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,06</t>
+          <t>1,37; 4,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,73</t>
+          <t>0,43; 2,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,46</t>
+          <t>0,55; 3,37</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,67</t>
+          <t>0,64; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,1</t>
+          <t>1,37; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,98</t>
+          <t>1,83; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,52</t>
+          <t>0,84; 3,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,11</t>
+          <t>1,34; 4,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>1,44; 3,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,74</t>
+          <t>1,0; 2,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,55</t>
+          <t>1,66; 3,63</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2636</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7131</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4344</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>592; 6121</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>785; 7592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1858; 8779</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>707; 7202</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1878; 9309</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2562; 10441</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2138; 9884</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3485; 12538</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5955</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5287</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3628</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1929; 9110</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4067</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>625; 7671</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4602</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>618; 6336</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>663; 7850</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2667; 10656</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2083</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>644; 5923</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>606; 5885</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4918</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2705; 10670</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4941</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>707; 6739</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4609; 14161</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1223; 7471</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1482; 9077</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17458</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2232; 10004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2516; 11014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4764; 14960</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6609; 17076</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3037; 12290</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4781; 15423</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10249; 22854</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7098; 19184</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11667; 25541</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,51</t>
+          <t>0,0; 78,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,46</t>
+          <t>0,0; 65,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,1</t>
+          <t>0,77; 9,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,66</t>
+          <t>1,19; 11,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,92</t>
+          <t>2,37; 11,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,01</t>
+          <t>0,8; 8,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,6</t>
+          <t>2,29; 10,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,34</t>
+          <t>1,58; 6,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,27; 6,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,63</t>
+          <t>2,23; 8,69</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,36</t>
+          <t>1,33; 6,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,86</t>
+          <t>0,48; 5,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,09</t>
+          <t>0,3; 2,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,08</t>
+          <t>0,26; 2,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,71</t>
+          <t>0,91; 3,55</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,62</t>
+          <t>0,38; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,09</t>
+          <t>0,42; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,14</t>
+          <t>1,58; 6,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,14</t>
+          <t>0,54; 5,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,2</t>
+          <t>1,38; 3,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,64</t>
+          <t>0,45; 2,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,37</t>
+          <t>0,55; 3,39</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,55; 2,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,77; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,31</t>
+          <t>1,41; 4,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,72</t>
+          <t>1,93; 4,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,41</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,33</t>
+          <t>1,32; 4,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,21</t>
+          <t>1,47; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,71</t>
+          <t>1,0; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,63</t>
+          <t>1,62; 3,58</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2622</t>
+          <t>0; 2600</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2636</t>
+          <t>0; 2604</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 4138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>592; 6121</t>
+          <t>585; 7140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>785; 7592</t>
+          <t>773; 7289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1858; 8779</t>
+          <t>1902; 9062</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>707; 7202</t>
+          <t>723; 7444</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1878; 9309</t>
+          <t>1838; 8557</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2562; 10441</t>
+          <t>2603; 10495</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2138; 9884</t>
+          <t>2097; 10245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3485; 12538</t>
+          <t>3245; 12636</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5287</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1929; 9110</t>
+          <t>1909; 8684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4067</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>625; 7671</t>
+          <t>626; 7317</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4602</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>618; 6336</t>
+          <t>614; 6050</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>663; 7850</t>
+          <t>670; 7394</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2667; 10656</t>
+          <t>2620; 10177</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>644; 5923</t>
+          <t>628; 5746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>606; 5885</t>
+          <t>607; 6010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4918</t>
+          <t>0; 5332</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2705; 10670</t>
+          <t>2738; 10720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4941</t>
+          <t>0; 4801</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>707; 6739</t>
+          <t>712; 6716</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4609; 14161</t>
+          <t>4640; 13367</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1223; 7471</t>
+          <t>1278; 7729</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1482; 9077</t>
+          <t>1490; 9127</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2232; 10004</t>
+          <t>1936; 9331</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2516; 11014</t>
+          <t>2675; 11731</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4764; 14960</t>
+          <t>4889; 14753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6609; 17076</t>
+          <t>6994; 17441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3037; 12290</t>
+          <t>3127; 12029</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4781; 15423</t>
+          <t>4692; 15426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10249; 22854</t>
+          <t>10510; 23692</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7098; 19184</t>
+          <t>7083; 19105</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11667; 25541</t>
+          <t>11418; 25186</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,84%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,22 +698,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 76,67</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,65</t>
+          <t>0,0; 65,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>2,4; 10,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 9,45</t>
+          <t>0,91; 7,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,19</t>
+          <t>2,25; 11,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 11,27</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,28</t>
+          <t>0,77; 9,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,66</t>
+          <t>1,18; 11,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,37</t>
+          <t>1,53; 6,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,19</t>
+          <t>1,27; 6,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,69</t>
+          <t>1,97; 8,48</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,48; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,06</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,59</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>1,21; 6,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,95</t>
+          <t>0,3; 3,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,9</t>
+          <t>0,26; 2,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,55</t>
+          <t>1,02; 3,92</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,51</t>
+          <t>1,54; 6,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,18</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,55; 5,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,17</t>
+          <t>0,39; 3,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,42; 4,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,12</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,96</t>
+          <t>1,24; 4,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,39</t>
+          <t>0,63; 3,46</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,66</t>
+          <t>1,97; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,39</t>
+          <t>0,82; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,25</t>
+          <t>1,22; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,82</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,34</t>
+          <t>0,72; 2,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,33</t>
+          <t>1,2; 4,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,32</t>
+          <t>1,5; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,7</t>
+          <t>1,05; 2,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,58</t>
+          <t>1,62; 3,55</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>621</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2600</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1437,22 +1437,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0; 2528</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2604</t>
+          <t>0; 2595</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2279</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2771</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2862</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>1931; 8309</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>585; 7140</t>
+          <t>822; 7001</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>773; 7289</t>
+          <t>1808; 8991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1902; 9062</t>
+          <t>0; 4311</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>723; 7444</t>
+          <t>581; 6868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1838; 8557</t>
+          <t>766; 7445</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2603; 10495</t>
+          <t>2514; 10340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2097; 10245</t>
+          <t>2096; 10872</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3245; 12636</t>
+          <t>2864; 12330</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4590</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5503</t>
+          <t>0; 3250</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>623; 6570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1909; 8684</t>
+          <t>0; 4852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 5514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>626; 7317</t>
+          <t>0; 3340</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>1729; 8891</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>614; 6050</t>
+          <t>617; 6259</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>670; 7394</t>
+          <t>659; 7581</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2620; 10177</t>
+          <t>2924; 11246</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2097</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2083</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1481</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2892</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>628; 5746</t>
+          <t>2674; 10811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>607; 6010</t>
+          <t>0; 4839</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5332</t>
+          <t>719; 7239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2738; 10720</t>
+          <t>630; 5639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>609; 6232</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>712; 6716</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4640; 13367</t>
+          <t>4172; 13675</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1278; 7729</t>
+          <t>1261; 7730</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1490; 9127</t>
+          <t>1687; 9309</t>
         </is>
       </c>
     </row>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>8842</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1936; 9331</t>
+          <t>7123; 18017</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2675; 11731</t>
+          <t>2946; 12686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4889; 14753</t>
+          <t>4364; 14639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6994; 17441</t>
+          <t>2049; 9353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3127; 12029</t>
+          <t>2479; 10202</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4692; 15426</t>
+          <t>4151; 14237</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10510; 23692</t>
+          <t>10666; 23660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7083; 19105</t>
+          <t>7409; 19371</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11418; 25186</t>
+          <t>11379; 24982</t>
         </is>
       </c>
     </row>
